--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/karbon_ayakizi.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/karbon_ayakizi.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>51,1</t>
+          <t>66,8</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>18.659</t>
+          <t>24.375</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>10,5</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>365</v>
+        <v>476</v>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
